--- a/docs/StructureDefinition-RNDSRegistroEletronicoDispensacaoFornecimentoMedicamento.xlsx
+++ b/docs/StructureDefinition-RNDSRegistroEletronicoDispensacaoFornecimentoMedicamento.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4905" uniqueCount="623">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4906" uniqueCount="623">
   <si>
     <t>Property</t>
   </si>
@@ -51,7 +51,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>draft</t>
+    <t>active</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-25T14:13:05-03:00</t>
+    <t>2025-08-18T16:48:33-03:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -2182,7 +2182,9 @@
       <c r="A12" t="s" s="2">
         <v>21</v>
       </c>
-      <c r="B12" s="2"/>
+      <c r="B12" t="s" s="2">
+        <v>9</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
@@ -14104,7 +14106,7 @@
         <v>90</v>
       </c>
       <c r="H102" t="s" s="2">
-        <v>77</v>
+        <v>91</v>
       </c>
       <c r="I102" t="s" s="2">
         <v>77</v>
